--- a/event_planner_forms/007_dj_request_form--event_planner_forms.xlsx
+++ b/event_planner_forms/007_dj_request_form--event_planner_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="49" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -525,13 +525,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Request Title</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>Event Title</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Enter the title of the event</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -551,10 +555,14 @@
           <t>Event Name</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Enter the name of the event</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -574,10 +582,14 @@
           <t>Event Date</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter the date of the event</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -597,10 +609,14 @@
           <t>Start Time</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Enter the start time of the event</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -620,10 +636,14 @@
           <t>End Time</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter the end time of the event</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -643,10 +663,14 @@
           <t>Song Request</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Enter the songs you would like to hear</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -666,7 +690,11 @@
           <t>Artist Request</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Enter the artist you would like to request</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>no</t>
@@ -689,7 +717,11 @@
           <t>Genre Request</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enter the genre of music you would like to hear</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -699,43 +731,51 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>song_request</t>
+          <t>event_type</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Song Request</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Event Type</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Select the type of event</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>event_type</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Event Type</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Enter your email</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>no</t>
@@ -750,15 +790,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Phone</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Enter your phone number</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>no</t>
@@ -773,15 +817,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>phone</t>
+          <t>message</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Message</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Add a comment or message</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
@@ -796,18 +844,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>message</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Message</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Assigned Tool</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Enter the assigned tool</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -819,269 +871,20 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>form_comments</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Form Comments</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Add any comments for the DJ</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>form_comments</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Form Comments</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>form_comments</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Form Comments</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>form_comments</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Form Comments</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>form_comments</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Form Comments</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>form_comments</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Form Comments</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>form_comments</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Form Comments</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>form_comments</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Form Comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>form_comments</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Form Comments</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>form_comments</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Form Comments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>form_comments</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Form Comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>form_comments</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Form Comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
